--- a/results/Int Task Remove ACC 0.5/Rando_3_permute.xlsx
+++ b/results/Int Task Remove ACC 0.5/Rando_3_permute.xlsx
@@ -440,677 +440,677 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7068787812430852</v>
+        <v>0.7528578946221938</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7331945707167695</v>
+        <v>0.7510831394822255</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7372955391506628</v>
+        <v>0.7446507985824888</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7236437970129541</v>
+        <v>0.7657070989059116</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7230120850735985</v>
+        <v>0.7660229548755895</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7206056179942745</v>
+        <v>0.7681938197706346</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7369796831809849</v>
+        <v>0.7636216469681839</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.71197260365063</v>
+        <v>0.7678235058751504</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6895015437388863</v>
+        <v>0.780021508014487</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7102173387156872</v>
+        <v>0.6967633648348549</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6980296549201876</v>
+        <v>0.7003982880721091</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.711019876569678</v>
+        <v>0.6997665761327535</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6787842239401627</v>
+        <v>0.6523492002710285</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6685266436835111</v>
+        <v>0.6845808402112739</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6667117616508433</v>
+        <v>0.6592980316039407</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6489189241865418</v>
+        <v>0.6104165974000066</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6473900895746894</v>
+        <v>0.6006703484046121</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.629597252110388</v>
+        <v>0.5970405843392763</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.536271844793765</v>
+        <v>0.5949098463369307</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.536271844793765</v>
+        <v>0.5840658402055414</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.5301656782075432</v>
+        <v>0.5940826591059958</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.5215779499285168</v>
+        <v>0.571597268161145</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5215779499285168</v>
+        <v>0.6377149225035054</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5199585431874282</v>
+        <v>0.6451699259257561</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5199986700801277</v>
+        <v>0.6424476028767543</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5115158449634444</v>
+        <v>0.6149486433097578</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.5098213436088751</v>
+        <v>0.6469045541730248</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.5019702304315475</v>
+        <v>0.6487996899910918</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.5016543744618697</v>
+        <v>0.6648578992081244</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5061113257581403</v>
+        <v>0.5939571192559786</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.500511331261257</v>
+        <v>0.581177850413823</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.498024610396534</v>
+        <v>0.6121110987545759</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.498024610396534</v>
+        <v>0.5411805102535675</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.4980647372892335</v>
+        <v>0.512578634378658</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.50149902606299</v>
+        <v>0.5098964382223558</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5005514581539565</v>
+        <v>0.5266562948203061</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5005514581539565</v>
+        <v>0.5254977741039378</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5007469334455358</v>
+        <v>0.5521747056119179</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5020906111096461</v>
+        <v>0.5584012528762383</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5017747551399683</v>
+        <v>0.5584012528762383</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5017747551399683</v>
+        <v>0.6315130246161289</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5</v>
+        <v>0.6201525280515642</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5</v>
+        <v>0.6497770664489878</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5</v>
+        <v>0.6521835335283118</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.4996841440303222</v>
+        <v>0.6521835335283118</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.4996841440303222</v>
+        <v>0.5689798482744863</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.4996841440303222</v>
+        <v>0.5157360475927877</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.4996841440303222</v>
+        <v>0.5166434886091217</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.4987365761212887</v>
+        <v>0.5208648377211136</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.4987365761212887</v>
+        <v>0.5205489817514357</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.4990524320909665</v>
+        <v>0.5133295805134637</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.4990524320909665</v>
+        <v>0.5145528774994754</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.4990524320909665</v>
+        <v>0.5145528774994754</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.4990524320909665</v>
+        <v>0.4917011853484103</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.4987365761212887</v>
+        <v>0.4890189891921081</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.4993682880606444</v>
+        <v>0.4914306154433505</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.4993682880606444</v>
+        <v>0.48847269021007</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.4993682880606444</v>
+        <v>0.48847269021007</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.4993682880606444</v>
+        <v>0.4989761909948374</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.4996841440303222</v>
+        <v>0.504431155436678</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.4996841440303222</v>
+        <v>0.5032078584506663</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.4983805932589113</v>
+        <v>0.4934214825625722</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.4999598731073004</v>
+        <v>0.4934616094552717</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.4999598731073004</v>
+        <v>0.4934616094552717</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.4999598731073004</v>
+        <v>0.4852843219644292</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.4993281611679448</v>
+        <v>0.4843768809480953</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.4987365761212887</v>
+        <v>0.4843768809480953</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.4990524320909665</v>
+        <v>0.5059445125327751</v>
       </c>
     </row>
     <row r="70">
@@ -1120,207 +1120,207 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.4965255843335439</v>
+        <v>0.580299071463703</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.4981048641819331</v>
+        <v>0.5817178437412939</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.4974731522425774</v>
+        <v>0.5960918699475943</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.4974731522425774</v>
+        <v>0.5717268207004321</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.4895715938287132</v>
+        <v>0.5936957212121073</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4946252893435584</v>
+        <v>0.5905423206872475</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.4946252893435584</v>
+        <v>0.5755119331646475</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.471522517492459</v>
+        <v>0.5705436506071199</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.471522517492459</v>
+        <v>0.5733061005488213</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.471522517492459</v>
+        <v>0.499523636459524</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4745606965111386</v>
+        <v>0.5001152215061802</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.4828984915727793</v>
+        <v>0.4997993655365023</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4868091438870118</v>
+        <v>0.5050835040637077</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.4868091438870118</v>
+        <v>0.4974330253498778</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.4883884237354009</v>
+        <v>0.4980647372892335</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4772830195601405</v>
+        <v>0.4939586096834218</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4769671635904627</v>
+        <v>0.5005462989820381</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4695070009962934</v>
+        <v>0.5005462989820381</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4695070009962934</v>
+        <v>0.4979443566111349</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4999948408280815</v>
+        <v>0.4988919245201684</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4980194512246154</v>
+        <v>0.5021255788304272</v>
       </c>
     </row>
   </sheetData>
